--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>132100623</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>132082923</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>132100625</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>132100623</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>132082923</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132100624</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>132100625</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132100623</v>
+        <v>132082923</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595872</v>
+        <v>595921</v>
       </c>
       <c r="R9" t="n">
-        <v>6969358</v>
+        <v>6969277</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,19 +1475,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132082923</v>
+        <v>132100623</v>
       </c>
       <c r="B10" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,13 +1539,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595921</v>
+        <v>595872</v>
       </c>
       <c r="R10" t="n">
-        <v>6969277</v>
+        <v>6969358</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,9 +1572,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,7 +1614,7 @@
         <v>132100624</v>
       </c>
       <c r="B11" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132082923</v>
+        <v>132100623</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595921</v>
+        <v>595872</v>
       </c>
       <c r="R9" t="n">
-        <v>6969277</v>
+        <v>6969358</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,9 +1475,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132100623</v>
+        <v>132082923</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1539,13 +1549,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595872</v>
+        <v>595921</v>
       </c>
       <c r="R10" t="n">
-        <v>6969358</v>
+        <v>6969277</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,19 +1582,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132100623</v>
+        <v>132082923</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595872</v>
+        <v>595921</v>
       </c>
       <c r="R9" t="n">
-        <v>6969358</v>
+        <v>6969277</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,19 +1475,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1504,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132082923</v>
+        <v>132100623</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1549,13 +1539,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595921</v>
+        <v>595872</v>
       </c>
       <c r="R10" t="n">
-        <v>6969277</v>
+        <v>6969358</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,9 +1572,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>132100625</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>132100623</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>132082923</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132100624</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117192140</v>
+        <v>117192138</v>
       </c>
       <c r="B2" t="n">
-        <v>90485</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595939</v>
+        <v>595942</v>
       </c>
       <c r="R2" t="n">
-        <v>6969370</v>
+        <v>6969396</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117192137</v>
+        <v>117192140</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595947</v>
+        <v>595939</v>
       </c>
       <c r="R3" t="n">
-        <v>6969383</v>
+        <v>6969370</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117192139</v>
+        <v>132082923</v>
       </c>
       <c r="B4" t="n">
-        <v>79064</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häbberåsknulen, Mpd</t>
+          <t>Rismyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595943</v>
+        <v>595921</v>
       </c>
       <c r="R4" t="n">
-        <v>6969356</v>
+        <v>6969277</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117772736</v>
+        <v>132100623</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Rismyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596092</v>
+        <v>595872</v>
       </c>
       <c r="R5" t="n">
-        <v>6969666</v>
+        <v>6969358</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1061,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117772737</v>
+        <v>117192139</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Häbberåsknulen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596098</v>
+        <v>595943</v>
       </c>
       <c r="R6" t="n">
-        <v>6969661</v>
+        <v>6969356</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,27 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117772738</v>
+        <v>117192137</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Häbberåsknulen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596098</v>
+        <v>595947</v>
       </c>
       <c r="R7" t="n">
-        <v>6969661</v>
+        <v>6969383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,68 +1255,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132100625</v>
+        <v>117192136</v>
       </c>
       <c r="B8" t="n">
-        <v>57951</v>
+        <v>92183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rismyran, Mpd</t>
+          <t>Häbberåsknulen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595716</v>
+        <v>595360</v>
       </c>
       <c r="R8" t="n">
-        <v>6969605</v>
+        <v>6969854</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1360,27 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132100623</v>
+        <v>117772736</v>
       </c>
       <c r="B9" t="n">
-        <v>79328</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,37 +1375,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rismyran, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595872</v>
+        <v>596092</v>
       </c>
       <c r="R9" t="n">
-        <v>6969358</v>
+        <v>6969666</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1472,22 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,22 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132082923</v>
+        <v>117772738</v>
       </c>
       <c r="B10" t="n">
-        <v>79328</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,34 +1472,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rismyran, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595921</v>
+        <v>596098</v>
       </c>
       <c r="R10" t="n">
-        <v>6969277</v>
+        <v>6969661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,68 +1546,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100624</v>
+        <v>117772737</v>
       </c>
       <c r="B11" t="n">
-        <v>57954</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rismyran, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595752</v>
+        <v>596098</v>
       </c>
       <c r="R11" t="n">
-        <v>6969608</v>
+        <v>6969661</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1684,27 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,15 +1643,255 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132100625</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rismyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595716</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6969605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132100624</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rismyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595752</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6969608</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20628-2025 artfynd.xlsx
+++ b/artfynd/A 20628-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192140</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100623</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192139</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100625</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100624</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192137</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772736</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772738</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,8 +1952,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>